--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2358B3-5757-433F-BFB7-C2D58F2DB6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FBEF2D-D17F-4E11-B695-48E6E0F5C418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7368" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="134">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -2844,6 +2844,9 @@
       </rPr>
       <t>Utiliser des fils d'Ariane pour permettre aux utilisateurs de voir où ils se trouvent et de revenir rapidement aux pages précédentes.</t>
     </r>
+  </si>
+  <si>
+    <t>Elouan LUCAS</t>
   </si>
 </sst>
 </file>
@@ -2889,7 +2892,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2899,6 +2902,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2930,7 +2951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2943,6 +2964,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3224,32 +3248,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H203"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" customWidth="1"/>
+    <col min="2" max="2" width="7.6328125" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" customWidth="1"/>
+    <col min="4" max="4" width="255.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="C1" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C2" s="3"/>
       <c r="D2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
@@ -3257,7 +3284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
@@ -3265,1121 +3292,1158 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C8" s="3"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="6"/>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B9" s="7"/>
       <c r="C9" s="3"/>
       <c r="D9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C10" s="3"/>
       <c r="D10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="3"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B12" s="6"/>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="3"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B13" s="6"/>
+      <c r="C13" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="3"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="6"/>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C15" s="3"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B15" s="6"/>
+      <c r="C15" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C16" s="3"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B16" s="8"/>
+      <c r="C16" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C17" s="3"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="6"/>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C18" s="3"/>
       <c r="D18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C20" s="3"/>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="6"/>
+      <c r="C20" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C21" s="3"/>
       <c r="D21" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C22" s="4"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C25" s="3"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="6"/>
+      <c r="C25" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C26" s="3"/>
       <c r="D26" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C27" s="3"/>
       <c r="D27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C28" s="3"/>
       <c r="D28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C29" s="3"/>
       <c r="D29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C30" s="3"/>
       <c r="D30" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C32" s="3"/>
       <c r="D32" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C33" s="3"/>
       <c r="D33" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C34" s="3"/>
       <c r="D34" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C35" s="3"/>
       <c r="D35" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C36" s="4"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C39" s="3"/>
       <c r="D39" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C40" s="3"/>
       <c r="D40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C41" s="3"/>
       <c r="D41" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C42" s="3"/>
       <c r="D42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C43" s="3"/>
       <c r="D43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C44" s="3"/>
       <c r="D44" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C45" s="3"/>
       <c r="D45" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C46" s="3"/>
       <c r="D46" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C48" s="3"/>
       <c r="D48" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C49" s="3"/>
       <c r="D49" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C50" s="3"/>
       <c r="D50" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C52" s="3"/>
       <c r="D52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C53" s="3"/>
       <c r="D53" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C54" s="3"/>
       <c r="D54" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C55" s="3"/>
       <c r="D55" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C56" s="3"/>
       <c r="D56" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C57" s="3"/>
       <c r="D57" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C58" s="3"/>
       <c r="D58" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C59" s="4"/>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C62" s="3"/>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B62" s="6"/>
+      <c r="C62" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D62" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C63" s="3"/>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B63" s="6"/>
+      <c r="C63" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D63" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C65" s="3"/>
       <c r="D65" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C66" s="3"/>
       <c r="D66" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C67" s="3"/>
       <c r="D67" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C68" s="3"/>
       <c r="D68" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C69" s="3"/>
       <c r="D69" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C70" s="3"/>
       <c r="D70" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B71" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C72" s="3"/>
       <c r="D72" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C73" s="3"/>
       <c r="D73" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C74" s="3"/>
       <c r="D74" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C75" s="3"/>
       <c r="D75" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C76" s="3"/>
       <c r="D76" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C77" s="3"/>
       <c r="D77" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C78" s="4"/>
       <c r="D78" s="2"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B80" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C81" s="3"/>
       <c r="D81" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C82" s="3"/>
       <c r="D82" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B83" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C84" s="3"/>
       <c r="D84" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C85" s="3"/>
       <c r="D85" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B86" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C87" s="3"/>
       <c r="D87" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C88" s="3"/>
       <c r="D88" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C89" s="3"/>
       <c r="D89" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C90" s="3"/>
       <c r="D90" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C91" s="3"/>
       <c r="D91" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C92" s="4"/>
       <c r="D92" s="2"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C95" s="3"/>
       <c r="D95" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C96" s="3"/>
       <c r="D96" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C97" s="3"/>
       <c r="D97" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B98" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C99" s="3"/>
       <c r="D99" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C100" s="3"/>
       <c r="D100" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C101" s="3"/>
       <c r="D101" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C102" s="3"/>
       <c r="D102" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C103" s="4"/>
       <c r="D103" s="2"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B105" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C106" s="3"/>
       <c r="D106" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C107" s="3"/>
       <c r="D107" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C108" s="3"/>
       <c r="D108" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B109" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C110" s="3"/>
       <c r="D110" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C111" s="3"/>
       <c r="D111" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C112" s="3"/>
       <c r="D112" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C113" s="4"/>
       <c r="D113" s="2"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B115" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C116" s="3"/>
       <c r="D116" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C117" s="3"/>
       <c r="D117" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C118" s="3"/>
       <c r="D118" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B119" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C120" s="3"/>
       <c r="D120" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C121" s="3"/>
       <c r="D121" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C122" s="3"/>
       <c r="D122" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C123" s="4"/>
       <c r="D123" s="2"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B125" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C126" s="3"/>
       <c r="D126" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C127" s="3"/>
       <c r="D127" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C128" s="3"/>
       <c r="D128" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C129" s="3"/>
       <c r="D129" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C130" s="3"/>
       <c r="D130" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C131" s="3"/>
       <c r="D131" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B132" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C133" s="3"/>
       <c r="D133" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C134" s="3"/>
       <c r="D134" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C135" s="3"/>
       <c r="D135" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C136" s="4"/>
       <c r="D136" s="2"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B138" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C139" s="3"/>
       <c r="D139" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C140" s="3"/>
       <c r="D140" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C141" s="3"/>
       <c r="D141" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C142" s="3"/>
       <c r="D142" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C143" s="4"/>
       <c r="D143" s="2"/>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C146" s="3"/>
       <c r="D146" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C147" s="3"/>
       <c r="D147" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C148" s="3"/>
       <c r="D148" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C150" s="3"/>
       <c r="D150" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C151" s="3"/>
       <c r="D151" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C152" s="3"/>
       <c r="D152" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C153" s="3"/>
       <c r="D153" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C154" s="4"/>
       <c r="D154" s="2"/>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B156" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C157" s="3"/>
       <c r="D157" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C158" s="3"/>
       <c r="D158" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C159" s="3"/>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B159" s="6"/>
+      <c r="C159" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D159" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C160" s="3"/>
       <c r="D160" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C161" s="3"/>
       <c r="D161" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C162" s="3"/>
       <c r="D162" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C163" s="3"/>
       <c r="D163" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C164" s="3"/>
       <c r="D164" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C165" s="3"/>
       <c r="D165" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B166" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C167" s="3"/>
       <c r="D167" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C168" s="3"/>
       <c r="D168" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C169" s="4"/>
       <c r="D169" s="2"/>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C171" s="3"/>
       <c r="D171" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C172" s="3"/>
       <c r="D172" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C173" s="3"/>
       <c r="D173" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C174" s="3"/>
       <c r="D174" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C175" s="3"/>
       <c r="D175" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C176" s="3"/>
       <c r="D176" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C177" s="3"/>
       <c r="D177" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C178" s="3"/>
       <c r="D178" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C179" s="3"/>
       <c r="D179" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C180" s="3"/>
       <c r="D180" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C181" s="4"/>
       <c r="D181" s="2"/>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C183" s="3"/>
       <c r="D183" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C184" s="3"/>
       <c r="D184" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C185" s="3"/>
       <c r="D185" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C186" s="3"/>
       <c r="D186" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C187" s="3"/>
       <c r="D187" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C188" s="3"/>
       <c r="D188" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C189" s="3"/>
       <c r="D189" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C190" s="4"/>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" s="2"/>
       <c r="B192" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C192" s="2"/>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C193" s="3"/>
       <c r="D193" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C194" s="3"/>
       <c r="D194" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C195" s="3"/>
       <c r="D195" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" s="2"/>
       <c r="B196" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C196" s="2"/>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C197" s="3"/>
       <c r="D197" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C198" s="3"/>
       <c r="D198" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C199" s="3"/>
       <c r="D199" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B200" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C201" s="3"/>
       <c r="D201" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C202" s="3"/>
       <c r="D202" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C203" s="3"/>
       <c r="D203" s="2" t="s">
         <v>13</v>
@@ -4398,24 +4462,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2646D6AF-1D80-493F-A7C9-967D3419C648}">
   <dimension ref="A3:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3">
         <f>COUNTIF(Feuil1!C7:'Feuil1'!C229,"P")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4">
         <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FBEF2D-D17F-4E11-B695-48E6E0F5C418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F17E95-9161-4306-9ECE-034BC719259E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="134">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -2961,12 +2961,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3257,18 +3257,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C2" s="3"/>
@@ -3303,7 +3303,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="6"/>
+      <c r="B8" s="5"/>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
@@ -3312,7 +3312,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B9" s="7"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="3"/>
       <c r="D9" t="s">
         <v>20</v>
@@ -3330,7 +3330,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B12" s="6"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
@@ -3339,7 +3339,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B13" s="6"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
@@ -3348,7 +3348,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B14" s="6"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="3" t="s">
         <v>9</v>
       </c>
@@ -3357,7 +3357,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="6"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
         <v>9</v>
       </c>
@@ -3366,7 +3366,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="8"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="3" t="s">
         <v>11</v>
       </c>
@@ -3375,7 +3375,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="6"/>
+      <c r="B17" s="5"/>
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
@@ -3395,7 +3395,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="6"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
@@ -3424,7 +3424,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B25" s="6"/>
+      <c r="B25" s="5"/>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
@@ -3433,25 +3433,37 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C26" s="3"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C27" s="3"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D27" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C28" s="3"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D28" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C29" s="3"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D29" t="s">
         <v>35</v>
       </c>
@@ -3468,19 +3480,28 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C32" s="3"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D32" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C33" s="3"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D33" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C34" s="3"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D34" t="s">
         <v>38</v>
       </c>
@@ -3638,7 +3659,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B62" s="6"/>
+      <c r="B62" s="5"/>
       <c r="C62" s="3" t="s">
         <v>9</v>
       </c>
@@ -3647,7 +3668,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B63" s="6"/>
+      <c r="B63" s="5"/>
       <c r="C63" s="3" t="s">
         <v>9</v>
       </c>
@@ -3661,18 +3682,25 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C65" s="3"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D65" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C66" s="3"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D66" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B67" s="6"/>
       <c r="C67" s="3"/>
       <c r="D67" t="s">
         <v>60</v>
@@ -4185,7 +4213,7 @@
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B159" s="6"/>
+      <c r="B159" s="5"/>
       <c r="C159" s="3" t="s">
         <v>9</v>
       </c>
@@ -4479,7 +4507,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F17E95-9161-4306-9ECE-034BC719259E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F47F166-ECCD-43DF-BEEB-7344FAA955E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="134">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -2951,7 +2951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2966,6 +2966,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3527,42 +3530,51 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="9">
+        <v>1</v>
+      </c>
       <c r="C39" s="3"/>
       <c r="D39" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="9"/>
       <c r="C40" s="3"/>
       <c r="D40" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="9"/>
       <c r="C41" s="3"/>
       <c r="D41" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
       <c r="C42" s="3"/>
       <c r="D42" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
       <c r="C43" s="3"/>
       <c r="D43" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
       <c r="C44" s="3"/>
       <c r="D44" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="9"/>
       <c r="C45" s="3"/>
       <c r="D45" t="s">
         <v>54</v>
@@ -3707,13 +3719,19 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C68" s="3"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D68" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C69" s="3"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D69" t="s">
         <v>62</v>
       </c>
@@ -3730,31 +3748,46 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C72" s="3"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D72" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C73" s="3"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D73" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C74" s="3"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D74" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C75" s="3"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D75" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C76" s="3"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D76" t="s">
         <v>67</v>
       </c>
@@ -4478,9 +4511,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A39:A45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4489,25 +4523,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2646D6AF-1D80-493F-A7C9-967D3419C648}">
-  <dimension ref="A3:B4"/>
+  <dimension ref="A3:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3">
         <f>COUNTIF(Feuil1!C7:'Feuil1'!C229,"P")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4">
         <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <f>B4*0.25+B3*0.125</f>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>

--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F47F166-ECCD-43DF-BEEB-7344FAA955E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFE3DBC-2C55-419F-AD6C-26FA9D7A36C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="134">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -3530,52 +3530,64 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="9">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D39" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="9"/>
-      <c r="C40" s="3"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D40" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="9"/>
-      <c r="C41" s="3"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D41" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="9"/>
-      <c r="C42" s="3"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D42" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="9"/>
-      <c r="C43" s="3"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D43" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="9"/>
-      <c r="C44" s="3"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D44" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="9"/>
-      <c r="C45" s="3"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D45" t="s">
         <v>54</v>
       </c>
@@ -3592,13 +3604,21 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C48" s="3"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D48" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C49" s="3"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D49" t="s">
         <v>47</v>
       </c>
@@ -3666,9 +3686,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B61" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B62" s="5"/>
@@ -4240,7 +4258,10 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C158" s="3"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D158" t="s">
         <v>102</v>
       </c>
@@ -4261,7 +4282,10 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C161" s="3"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D161" t="s">
         <v>103</v>
       </c>
@@ -4317,31 +4341,46 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C171" s="3"/>
+      <c r="B171" s="5"/>
+      <c r="C171" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D171" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C172" s="3"/>
+      <c r="B172" s="7"/>
+      <c r="C172" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D172" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C173" s="3"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D173" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C174" s="3"/>
+      <c r="B174" s="5"/>
+      <c r="C174" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D174" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C175" s="3"/>
+      <c r="B175" s="5"/>
+      <c r="C175" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D175" t="s">
         <v>114</v>
       </c>
@@ -4353,7 +4392,10 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C177" s="3"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D177" t="s">
         <v>116</v>
       </c>
@@ -4365,7 +4407,10 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C179" s="3"/>
+      <c r="B179" s="7"/>
+      <c r="C179" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D179" t="s">
         <v>118</v>
       </c>
@@ -4386,13 +4431,19 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C183" s="3"/>
+      <c r="B183" s="5"/>
+      <c r="C183" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D183" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C184" s="3"/>
+      <c r="B184" s="5"/>
+      <c r="C184" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D184" t="s">
         <v>121</v>
       </c>
@@ -4514,7 +4565,7 @@
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:H1"/>
-    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="A48:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4523,7 +4574,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2646D6AF-1D80-493F-A7C9-967D3419C648}">
-  <dimension ref="A3:C4"/>
+  <dimension ref="A3:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -4532,7 +4583,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Feuil1!C7:'Feuil1'!C229,"P")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -4541,11 +4592,17 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <f>B4*0.25+B3*0.125</f>
-        <v>6.75</v>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <f>20/0.25</f>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFE3DBC-2C55-419F-AD6C-26FA9D7A36C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D53A583-663B-4DD3-8588-CE62CEC5A011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="134">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -2951,7 +2951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2966,9 +2966,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3604,7 +3601,6 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="9"/>
       <c r="B48" s="5"/>
       <c r="C48" s="3" t="s">
         <v>9</v>
@@ -3614,7 +3610,6 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="9"/>
       <c r="B49" s="5"/>
       <c r="C49" s="3" t="s">
         <v>9</v>
@@ -3635,37 +3630,55 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C52" s="3"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D52" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C53" s="3"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D53" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C54" s="3"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D54" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C55" s="3"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D55" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C56" s="3"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D56" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C57" s="3"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D57" t="s">
         <v>50</v>
       </c>
@@ -4562,10 +4575,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:H1"/>
-    <mergeCell ref="A48:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4583,7 +4595,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Feuil1!C7:'Feuil1'!C229,"P")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -4592,11 +4604,11 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <f>B4*0.25+B3*0.125</f>
-        <v>11.5</v>
+        <v>12.875</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">

--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D53A583-663B-4DD3-8588-CE62CEC5A011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E1D2E1-0A14-4758-A4B9-7521D031B160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="134">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -2951,7 +2951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2966,6 +2966,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3844,7 +3847,10 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C81" s="3"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D81" t="s">
         <v>68</v>
       </c>
@@ -3861,7 +3867,10 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C84" s="3"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D84" t="s">
         <v>69</v>
       </c>
@@ -3878,25 +3887,37 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C87" s="3"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D87" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C88" s="3"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D88" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C89" s="3"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D89" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C90" s="3"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D90" t="s">
         <v>73</v>
       </c>
@@ -3918,17 +3939,29 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C95" s="3"/>
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" s="5"/>
+      <c r="C95" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D95" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C96" s="3"/>
+      <c r="A96">
+        <v>1</v>
+      </c>
+      <c r="B96" s="5"/>
+      <c r="C96" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D96" t="s">
         <v>76</v>
       </c>
@@ -3945,18 +3978,25 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" s="9">
+        <v>1</v>
+      </c>
       <c r="C99" s="3"/>
       <c r="D99" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" s="9"/>
       <c r="C100" s="3"/>
       <c r="D100" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>1</v>
+      </c>
       <c r="C101" s="3"/>
       <c r="D101" t="s">
         <v>79</v>
@@ -4304,19 +4344,28 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C162" s="3"/>
+      <c r="B162" s="7"/>
+      <c r="C162" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D162" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C163" s="3"/>
+      <c r="B163" s="7"/>
+      <c r="C163" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D163" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C164" s="3"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D164" t="s">
         <v>106</v>
       </c>
@@ -4575,9 +4624,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A99:A100"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4595,7 +4645,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Feuil1!C7:'Feuil1'!C229,"P")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -4604,11 +4654,11 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <f>B4*0.25+B3*0.125</f>
-        <v>12.875</v>
+        <v>15.125</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">

--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E1D2E1-0A14-4758-A4B9-7521D031B160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8712987-CF62-414E-AAA6-95DB7FB7D244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="134">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -3943,9 +3943,6 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95">
-        <v>1</v>
-      </c>
       <c r="B95" s="5"/>
       <c r="C95" s="3" t="s">
         <v>9</v>
@@ -3955,9 +3952,6 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96">
-        <v>1</v>
-      </c>
       <c r="B96" s="5"/>
       <c r="C96" s="3" t="s">
         <v>9</v>
@@ -3978,26 +3972,30 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" s="9">
-        <v>1</v>
-      </c>
-      <c r="C99" s="3"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D99" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="9"/>
-      <c r="C100" s="3"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D100" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>1</v>
-      </c>
-      <c r="C101" s="3"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D101" t="s">
         <v>79</v>
       </c>
@@ -4133,31 +4131,55 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C126" s="3"/>
+      <c r="A126" s="9">
+        <v>1</v>
+      </c>
+      <c r="B126" s="5"/>
+      <c r="C126" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D126" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C127" s="3"/>
+      <c r="A127" s="9"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D127" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C128" s="3"/>
+      <c r="A128" s="9">
+        <v>1</v>
+      </c>
+      <c r="B128" s="5"/>
+      <c r="C128" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D128" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C129" s="3"/>
+      <c r="A129" s="9"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D129" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C130" s="3"/>
+      <c r="A130" s="9"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D130" t="s">
         <v>90</v>
       </c>
@@ -4174,13 +4196,23 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C133" s="3"/>
+      <c r="A133" s="9">
+        <v>1</v>
+      </c>
+      <c r="B133" s="5"/>
+      <c r="C133" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D133" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C134" s="3"/>
+      <c r="A134" s="9"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D134" t="s">
         <v>92</v>
       </c>
@@ -4624,10 +4656,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="A133:A134"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:H1"/>
     <mergeCell ref="A99:A100"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A126:A127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4645,7 +4680,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Feuil1!C7:'Feuil1'!C229,"P")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -4654,11 +4689,11 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <f>B4*0.25+B3*0.125</f>
-        <v>15.125</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">

--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8712987-CF62-414E-AAA6-95DB7FB7D244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539DCF43-43B9-42E5-B35F-0DBDD80762DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="138">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -2847,13 +2847,25 @@
   </si>
   <si>
     <t>Elouan LUCAS</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>Pouvoire lancer tout le projet via un docker compose</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>Avoire une photo de profile lier a l'aplie</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2891,8 +2903,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2920,6 +2939,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2951,7 +2976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2964,11 +2989,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3250,7 +3276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.54296875" customWidth="1"/>
@@ -3260,18 +3286,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C2" s="3"/>
@@ -4276,12 +4302,18 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>1</v>
+      </c>
       <c r="C146" s="3"/>
       <c r="D146" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>1</v>
+      </c>
       <c r="C147" s="3"/>
       <c r="D147" t="s">
         <v>97</v>
@@ -4299,18 +4331,23 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" s="9">
+        <v>1</v>
+      </c>
       <c r="C150" s="3"/>
       <c r="D150" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" s="9"/>
       <c r="C151" s="3"/>
       <c r="D151" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" s="9"/>
       <c r="C152" s="3"/>
       <c r="D152" t="s">
         <v>100</v>
@@ -4337,6 +4374,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" s="8"/>
       <c r="C157" s="3"/>
       <c r="D157" t="s">
         <v>101</v>
@@ -4480,7 +4518,10 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C176" s="3"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D176" t="s">
         <v>115</v>
       </c>
@@ -4495,6 +4536,7 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178" s="8"/>
       <c r="C178" s="3"/>
       <c r="D178" t="s">
         <v>117</v>
@@ -4549,6 +4591,7 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A186" s="8"/>
       <c r="C186" s="3"/>
       <c r="D186" t="s">
         <v>123</v>
@@ -4655,9 +4698,30 @@
         <v>13</v>
       </c>
     </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D206" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="209" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D209" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A133:A134"/>
+    <mergeCell ref="A150:A152"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:H1"/>
     <mergeCell ref="A99:A100"/>
@@ -4671,10 +4735,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2646D6AF-1D80-493F-A7C9-967D3419C648}">
-  <dimension ref="A3:C6"/>
+  <dimension ref="A3:D6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -4683,20 +4747,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4">
         <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <f>B4*0.25+B3*0.125</f>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>17.75</v>
+      </c>
+      <c r="D4">
+        <f>(20-C4)/0.25</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6">
         <f>20/0.25</f>
         <v>80</v>

--- a/Fonctionnalités_Projet.xlsx
+++ b/Fonctionnalités_Projet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539DCF43-43B9-42E5-B35F-0DBDD80762DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2FA3C3-5B57-4C13-A60A-EFC396A58430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="148">
   <si>
     <t xml:space="preserve">NOM ELEVE : </t>
   </si>
@@ -2852,13 +2852,43 @@
     <t>Docker</t>
   </si>
   <si>
-    <t>Pouvoire lancer tout le projet via un docker compose</t>
-  </si>
-  <si>
-    <t>PP</t>
-  </si>
-  <si>
-    <t>Avoire une photo de profile lier a l'aplie</t>
+    <t>Back-end</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>Pouvoir lancer tout le Front-end</t>
+  </si>
+  <si>
+    <t>Pouvoir lancer tout le Back-end</t>
+  </si>
+  <si>
+    <t>Avoir une photo de profil liée à l'appli</t>
+  </si>
+  <si>
+    <t>Avoir un back-end simplifié avec des routes</t>
+  </si>
+  <si>
+    <t>Avoir les scripts SQL de création de la base de données</t>
+  </si>
+  <si>
+    <t>Avoir les scripts SQL de remplissage de la base de données</t>
+  </si>
+  <si>
+    <t>Photo de Profil</t>
+  </si>
+  <si>
+    <t>Github</t>
+  </si>
+  <si>
+    <t>Utiliser github</t>
+  </si>
+  <si>
+    <t>Styles</t>
+  </si>
+  <si>
+    <t>Avoire un css unique pour chaque page</t>
   </si>
 </sst>
 </file>
@@ -2905,13 +2935,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2939,12 +2968,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2976,7 +2999,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2989,13 +3012,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3276,7 +3305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.54296875" customWidth="1"/>
@@ -3998,7 +4027,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" s="9"/>
+      <c r="A99" s="11"/>
       <c r="B99" s="5"/>
       <c r="C99" s="3" t="s">
         <v>9</v>
@@ -4008,7 +4037,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" s="9"/>
+      <c r="A100" s="11"/>
       <c r="B100" s="5"/>
       <c r="C100" s="3" t="s">
         <v>9</v>
@@ -4157,9 +4186,6 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" s="9">
-        <v>1</v>
-      </c>
       <c r="B126" s="5"/>
       <c r="C126" s="3" t="s">
         <v>9</v>
@@ -4169,7 +4195,6 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" s="9"/>
       <c r="B127" s="5"/>
       <c r="C127" s="3" t="s">
         <v>9</v>
@@ -4179,9 +4204,6 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" s="9">
-        <v>1</v>
-      </c>
       <c r="B128" s="5"/>
       <c r="C128" s="3" t="s">
         <v>9</v>
@@ -4191,7 +4213,6 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" s="9"/>
       <c r="B129" s="5"/>
       <c r="C129" s="3" t="s">
         <v>9</v>
@@ -4201,7 +4222,6 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" s="9"/>
       <c r="B130" s="5"/>
       <c r="C130" s="3" t="s">
         <v>9</v>
@@ -4222,9 +4242,6 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" s="9">
-        <v>1</v>
-      </c>
       <c r="B133" s="5"/>
       <c r="C133" s="3" t="s">
         <v>9</v>
@@ -4234,7 +4251,6 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" s="9"/>
       <c r="B134" s="5"/>
       <c r="C134" s="3" t="s">
         <v>9</v>
@@ -4302,19 +4318,19 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146">
-        <v>1</v>
-      </c>
-      <c r="C146" s="3"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D146" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147">
-        <v>1</v>
-      </c>
-      <c r="C147" s="3"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D147" t="s">
         <v>97</v>
       </c>
@@ -4331,24 +4347,28 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" s="9">
-        <v>1</v>
-      </c>
-      <c r="C150" s="3"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D150" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" s="9"/>
-      <c r="C151" s="3"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D151" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" s="9"/>
-      <c r="C152" s="3"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D152" t="s">
         <v>100</v>
       </c>
@@ -4374,7 +4394,6 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A157" s="8"/>
       <c r="C157" s="3"/>
       <c r="D157" t="s">
         <v>101</v>
@@ -4482,10 +4501,7 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B172" s="7"/>
-      <c r="C172" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="C172" s="3"/>
       <c r="D172" t="s">
         <v>111</v>
       </c>
@@ -4536,17 +4552,13 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A178" s="8"/>
       <c r="C178" s="3"/>
       <c r="D178" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B179" s="7"/>
-      <c r="C179" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="C179" s="3"/>
       <c r="D179" t="s">
         <v>118</v>
       </c>
@@ -4591,7 +4603,6 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A186" s="8"/>
       <c r="C186" s="3"/>
       <c r="D186" t="s">
         <v>123</v>
@@ -4698,35 +4709,137 @@
         <v>13</v>
       </c>
     </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D204" s="12"/>
+    </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>134</v>
       </c>
+      <c r="D205" s="12"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D206" s="2" t="s">
+      <c r="B206" s="5"/>
+      <c r="C206" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B207" s="5"/>
+      <c r="C207" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C208" s="8"/>
+      <c r="D208" s="12"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>143</v>
+      </c>
+      <c r="C209" s="8"/>
+      <c r="D209" s="12"/>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B210" s="5"/>
+      <c r="C210" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C211" s="8"/>
+      <c r="D211" s="12"/>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A208" t="s">
+      <c r="C212" s="8"/>
+      <c r="D212" s="12"/>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B213" s="5"/>
+      <c r="C213" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C214" s="8"/>
+      <c r="D214" s="12"/>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D209" t="s">
-        <v>137</v>
+      <c r="C215" s="8"/>
+      <c r="D215" s="12"/>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B216" s="5"/>
+      <c r="C216" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B217" s="5"/>
+      <c r="C217" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D218" s="12"/>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>144</v>
+      </c>
+      <c r="D219" s="12"/>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B220" s="5"/>
+      <c r="C220" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D220" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>146</v>
+      </c>
+      <c r="B222" s="5"/>
+      <c r="C222" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D222" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A133:A134"/>
-    <mergeCell ref="A150:A152"/>
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:H1"/>
     <mergeCell ref="A99:A100"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A126:A127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4735,36 +4848,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2646D6AF-1D80-493F-A7C9-967D3419C648}">
-  <dimension ref="A3:D6"/>
+  <dimension ref="A3:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3">
-        <f>COUNTIF(Feuil1!C7:'Feuil1'!C229,"P")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <f>COUNTIF(Feuil1!C7:'Feuil1'!C231,"P")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4">
-        <f>COUNTIF(Feuil1!C8:'Feuil1'!C230,"X")</f>
-        <v>66</v>
+        <f>COUNTIF(Feuil1!C8:'Feuil1'!C232,"X")</f>
+        <v>78</v>
       </c>
       <c r="C4">
         <f>B4*0.25+B3*0.125</f>
-        <v>17.75</v>
-      </c>
-      <c r="D4">
-        <f>(20-C4)/0.25</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>20.625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6">
         <f>20/0.25</f>
         <v>80</v>
